--- a/docs/backend-integration/requests/2026-09-08-미회신-B2-C-D.xlsx
+++ b/docs/backend-integration/requests/2026-09-08-미회신-B2-C-D.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,17 +33,31 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A46"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,17 +65,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -864,27 +897,33 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>재검토 — 요청에서 제외:</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>· 경호계획 조치 5섹션 ↔ summary1~5: 섹션당 기간 1개라 summaryNDate와 일치 — 문제 없음. summaryN이 다중선택을 ", " join으로 받는 것만 소프트하나 항목 라벨에 쉼표가 없어 정상 동작.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>· 경호목록 지역청 필터: GetGuardCaseList.parentGroupName 이미 옴 → 프론트 미연동일 뿐. 섹션 B 마무리 후 프론트 후속작업.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A17:F17"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1106,34 +1145,41 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>재확인(요청 아님, 데이터 없어 재검증 예정):</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>· 종결 건 상태코드·totalGuardMinutes 실값 — 실서버에 정상 종결 건 0개. 오늘 날짜 경호건 생성→종결 후 GetHistoryList.statusName 종결 코드·totalMin 산출값 재확인.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>· GetHistoryList status/searchKey 파라미터 — 목록량 작아 클라 필터로 충분. 데이터 커지면 재검토.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>· [경찰서] 이력 상세 사건유형·5개 조치 — GetHistoryDetail에 caseType·summary1~5 없음. 종결 데이터 생기면 갭 확정 후, 남으면 findings #13(경찰 상세 조치)과 같은 성격으로 추가 요청.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1259,34 +1305,41 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>재검증 이월(요청 아님):</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>· 동래에 게스트 미부여 활성 경호건이 생기면 #17 상세 스코프 양성 테스트.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>· 종결/취소 터미널 데이터 재검증(#13·#14와 공통)도 게스트 목록에 동일 적용.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>· 아이디 미리보기 API 부재(구 findings #3)는 프론트 UX 변경(발급 후 목록 재조회)으로 해소 — 신규 EP 요청 안 함.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>